--- a/data/costs_outputs.xlsx
+++ b/data/costs_outputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aheller\Documents\GitHub\TEA.CART\inst\app\www\static_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qsi\Desktop\TEA-CART\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CF2255-0F05-4A9F-8F9E-D6A6422F7D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07631E1-FFB0-45EC-BD5E-649DDB92E652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{866DC24D-5F4B-4C41-856A-A432B225A869}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="774" activeTab="2" xr2:uid="{866DC24D-5F4B-4C41-856A-A432B225A869}"/>
   </bookViews>
   <sheets>
     <sheet name="bikeped" sheetId="1" r:id="rId1"/>
@@ -49,126 +49,276 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="100">
   <si>
     <t>Bicycle and Pedestrian</t>
   </si>
   <si>
+    <t>New shared-use path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core </t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Very High</t>
+  </si>
+  <si>
+    <t>Urban</t>
+  </si>
+  <si>
+    <t>Suburban</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Rural</t>
+  </si>
+  <si>
+    <t>New bicycle lane</t>
+  </si>
+  <si>
+    <t>New separated bike lane</t>
+  </si>
+  <si>
+    <t>New/improved sidewalk</t>
+  </si>
+  <si>
+    <t>New Complete Streets treatment</t>
+  </si>
+  <si>
+    <t>Widened shoulder</t>
+  </si>
+  <si>
+    <t>Transit: Increased Fixed Route Service</t>
+  </si>
+  <si>
+    <t>Bus: Diesel</t>
+  </si>
+  <si>
+    <t>GHG Increase</t>
+  </si>
+  <si>
+    <t>NOx Increase</t>
+  </si>
+  <si>
+    <t>PM2.5 Increase</t>
+  </si>
+  <si>
+    <t>Bus: CNG</t>
+  </si>
+  <si>
+    <t>Bus: Electric</t>
+  </si>
+  <si>
+    <t>Transit: Increased Demand Response Service</t>
+  </si>
+  <si>
+    <t>Demand Response: Gasoline</t>
+  </si>
+  <si>
+    <t>VMT Increase</t>
+  </si>
+  <si>
+    <t>Demand Response: Diesel</t>
+  </si>
+  <si>
+    <t>Demand Response: Electric</t>
+  </si>
+  <si>
+    <t>Transit: Fleet Electrification</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Demand Response: CNG</t>
+  </si>
+  <si>
+    <t>Public Transportation: Bus Priority Treatment</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>New Bus Priority</t>
+  </si>
+  <si>
+    <t>miles of treatment</t>
+  </si>
+  <si>
+    <t>Public Transportation: Rail</t>
+  </si>
+  <si>
+    <t>Light Rail / Streetcar</t>
+  </si>
+  <si>
+    <t>Electric</t>
+  </si>
+  <si>
+    <t>Heavy Rail</t>
+  </si>
+  <si>
+    <t>Commuter Rail</t>
+  </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Travel Demand Management</t>
+  </si>
+  <si>
+    <t>TDM program outreach</t>
+  </si>
+  <si>
+    <t># covered employees</t>
+  </si>
+  <si>
+    <t>Micromobility</t>
+  </si>
+  <si>
+    <t>E-bike subsidies</t>
+  </si>
+  <si>
+    <t>#bikes covered</t>
+  </si>
+  <si>
+    <t>Traffic Operations - Intersection</t>
+  </si>
+  <si>
+    <t>New or retimed signal</t>
+  </si>
+  <si>
+    <t>Urban Arterial</t>
+  </si>
+  <si>
+    <t>Active Trip Decrease</t>
+  </si>
+  <si>
+    <t>Rural Arterial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New roundabouts </t>
+  </si>
+  <si>
+    <t>New roundabouts</t>
+  </si>
+  <si>
+    <t>Medium and Heavy Duty Vehicle Replacement (Electrification)</t>
+  </si>
+  <si>
+    <t>Light Truck</t>
+  </si>
+  <si>
+    <t>Gasoline</t>
+  </si>
+  <si>
+    <t>Medium Truck</t>
+  </si>
+  <si>
+    <t>Heavy Truck</t>
+  </si>
+  <si>
+    <t>School Bus</t>
+  </si>
+  <si>
+    <t>Park and Ride</t>
+  </si>
+  <si>
+    <t>New/expanded park and ride</t>
+  </si>
+  <si>
+    <t>new spaces</t>
+  </si>
+  <si>
+    <t>EV Charging Infrastructure</t>
+  </si>
+  <si>
+    <t>Level 2: General public</t>
+  </si>
+  <si>
+    <t># new ports</t>
+  </si>
+  <si>
+    <t>DCFC (50kw): General public</t>
+  </si>
+  <si>
+    <t>DCFC (150kw): General public</t>
+  </si>
+  <si>
+    <t>DCFC: Dedicated truck/bus (50kw)</t>
+  </si>
+  <si>
+    <t>DCFC: Dedicated truck/bus (350kw)</t>
+  </si>
+  <si>
+    <t>Intermodal Freight Investment</t>
+  </si>
+  <si>
+    <t>Roadway Expansion</t>
+  </si>
+  <si>
+    <t>Urban Freeway</t>
+  </si>
+  <si>
+    <t>new lane-miles</t>
+  </si>
+  <si>
+    <t>Rural Freeway</t>
+  </si>
+  <si>
+    <t>VMT</t>
+  </si>
+  <si>
     <t>Facility Type</t>
   </si>
   <si>
     <t>Area Type</t>
   </si>
   <si>
-    <t>New shared-use path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core </t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Very High</t>
-  </si>
-  <si>
-    <t>Urban</t>
-  </si>
-  <si>
-    <t>Suburban</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Rural</t>
-  </si>
-  <si>
-    <t>New bicycle lane</t>
-  </si>
-  <si>
-    <t>New separated bike lane</t>
-  </si>
-  <si>
-    <t>New/improved sidewalk</t>
-  </si>
-  <si>
-    <t>New Complete Streets treatment</t>
-  </si>
-  <si>
-    <t>Widened shoulder</t>
-  </si>
-  <si>
-    <t>Transit: Increased Fixed Route Service</t>
-  </si>
-  <si>
-    <t>Bus: Diesel</t>
-  </si>
-  <si>
-    <t>GHG Increase</t>
-  </si>
-  <si>
-    <t>NOx Increase</t>
-  </si>
-  <si>
-    <t>PM2.5 Increase</t>
-  </si>
-  <si>
-    <t>Bus: CNG</t>
-  </si>
-  <si>
-    <t>Bus: Electric</t>
-  </si>
-  <si>
-    <t>Transit: Increased Demand Response Service</t>
-  </si>
-  <si>
-    <t>Vehicle &amp; Fuel Type</t>
-  </si>
-  <si>
-    <t>Demand Response: Gasoline</t>
-  </si>
-  <si>
-    <t>VMT Increase</t>
-  </si>
-  <si>
-    <t>Demand Response: Diesel</t>
-  </si>
-  <si>
-    <t>Demand Response: Electric</t>
-  </si>
-  <si>
-    <t>Transit: Fleet Electrification</t>
-  </si>
-  <si>
-    <t>***</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Demand Response: CNG</t>
-  </si>
-  <si>
-    <t>Public Transportation: Bus Priority Treatment</t>
+    <t>MT GHG</t>
+  </si>
+  <si>
+    <t>MT NOx</t>
+  </si>
+  <si>
+    <t>MT PM2.5</t>
+  </si>
+  <si>
+    <t>Daily Active Trips</t>
+  </si>
+  <si>
+    <t>Summary MT GHG</t>
+  </si>
+  <si>
+    <t>Summary VMT</t>
+  </si>
+  <si>
+    <t>Summary MT NOx</t>
+  </si>
+  <si>
+    <t>Summary MT PM2.5</t>
+  </si>
+  <si>
+    <t>Summary Daily Active Trips</t>
+  </si>
+  <si>
+    <t>Vehicle- Fuel Type</t>
   </si>
   <si>
     <t>Expanded Bus Priority</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>New Bus Priority</t>
-  </si>
-  <si>
-    <t>miles of treatment</t>
-  </si>
-  <si>
-    <t>Public Transportation: Rail</t>
+    <t>Vehicle Type-Fuel Type</t>
   </si>
   <si>
     <t>Vehicle Type</t>
@@ -177,172 +327,28 @@
     <t>Fuel Type</t>
   </si>
   <si>
-    <t>Light Rail / Streetcar</t>
-  </si>
-  <si>
-    <t>Electric</t>
-  </si>
-  <si>
-    <t>Heavy Rail</t>
-  </si>
-  <si>
-    <t>Commuter Rail</t>
-  </si>
-  <si>
-    <t>Diesel</t>
-  </si>
-  <si>
-    <t>Travel Demand Management</t>
-  </si>
-  <si>
     <t>Program Type</t>
   </si>
   <si>
-    <t>TDM program outreach</t>
-  </si>
-  <si>
-    <t># covered employees</t>
-  </si>
-  <si>
-    <t>Micromobility</t>
-  </si>
-  <si>
-    <t>E-bike subsidies</t>
-  </si>
-  <si>
-    <t>#bikes covered</t>
-  </si>
-  <si>
-    <t>Traffic Operations - Intersection</t>
-  </si>
-  <si>
     <t>Improvement Type</t>
   </si>
   <si>
     <t>Facility + Area Type</t>
   </si>
   <si>
-    <t>New or retimed signal</t>
-  </si>
-  <si>
-    <t>Urban Arterial</t>
-  </si>
-  <si>
-    <t>Active Trip Decrease</t>
-  </si>
-  <si>
-    <t>Rural Arterial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New roundabouts </t>
-  </si>
-  <si>
-    <t>New roundabouts</t>
-  </si>
-  <si>
-    <t>Medium and Heavy Duty Vehicle Replacement (Electrification)</t>
-  </si>
-  <si>
     <t>Replacement Vehicle Type</t>
   </si>
   <si>
     <t>Replacement Fuel Type</t>
   </si>
   <si>
-    <t>Light Truck</t>
-  </si>
-  <si>
-    <t>Gasoline</t>
-  </si>
-  <si>
-    <t>Medium Truck</t>
-  </si>
-  <si>
-    <t>Heavy Truck</t>
-  </si>
-  <si>
-    <t>School Bus</t>
-  </si>
-  <si>
-    <t>Park and Ride</t>
-  </si>
-  <si>
     <t>New/Expanded Park and Ride</t>
   </si>
   <si>
-    <t>New/expanded park and ride</t>
-  </si>
-  <si>
-    <t>new spaces</t>
-  </si>
-  <si>
-    <t>EV Charging Infrastructure</t>
-  </si>
-  <si>
     <t>Expanded Charging Ports</t>
   </si>
   <si>
-    <t>Level 2: General public</t>
-  </si>
-  <si>
-    <t># new ports</t>
-  </si>
-  <si>
-    <t>DCFC (50kw): General public</t>
-  </si>
-  <si>
-    <t>DCFC (150kw): General public</t>
-  </si>
-  <si>
-    <t>DCFC: Dedicated truck/bus (50kw)</t>
-  </si>
-  <si>
-    <t>DCFC: Dedicated truck/bus (350kw)</t>
-  </si>
-  <si>
-    <t>Intermodal Freight Investment</t>
-  </si>
-  <si>
-    <t>Roadway Expansion</t>
-  </si>
-  <si>
-    <t>Urban Freeway</t>
-  </si>
-  <si>
-    <t>new lane-miles</t>
-  </si>
-  <si>
-    <t>Rural Freeway</t>
-  </si>
-  <si>
-    <t>MT GHG</t>
-  </si>
-  <si>
-    <t>VMT</t>
-  </si>
-  <si>
-    <t>MT NOx</t>
-  </si>
-  <si>
-    <t>MT PM2.5</t>
-  </si>
-  <si>
-    <t>Daily Active Trips</t>
-  </si>
-  <si>
-    <t>Summary-MT GHG</t>
-  </si>
-  <si>
-    <t>Summary-VMT</t>
-  </si>
-  <si>
-    <t>Summary-MT NOx</t>
-  </si>
-  <si>
-    <t>Summary-MT PM2.5</t>
-  </si>
-  <si>
-    <t>Summary-Daily Active Trips</t>
+    <t>Vehicle  Fuel Type</t>
   </si>
 </sst>
 </file>
@@ -695,62 +701,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A8A278-740D-4C86-81F8-DC9D16E35DDF}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" customWidth="1"/>
-    <col min="3" max="13" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
       </c>
       <c r="C3">
         <v>-1227.9513483440437</v>
@@ -768,27 +773,27 @@
         <v>19622.093023255813</v>
       </c>
       <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
       </c>
       <c r="C4">
         <v>-674.3594178457821</v>
@@ -806,27 +811,27 @@
         <v>7350</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>-159.95142184763185</v>
@@ -844,27 +849,27 @@
         <v>1177.3255813953488</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>-39.363277578159305</v>
@@ -882,27 +887,27 @@
         <v>225</v>
       </c>
       <c r="H6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>-5053.9706756788928</v>
@@ -920,27 +925,27 @@
         <v>40909.090909090912</v>
       </c>
       <c r="H7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>-3380.0100180201689</v>
@@ -958,27 +963,27 @@
         <v>21818.18181818182</v>
       </c>
       <c r="H8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
         <v>7</v>
-      </c>
-      <c r="I8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
       </c>
       <c r="C9">
         <v>-1069.6234234241044</v>
@@ -996,27 +1001,27 @@
         <v>6818.181818181818</v>
       </c>
       <c r="H9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>-267.40585585602611</v>
@@ -1034,27 +1039,27 @@
         <v>1363.6363636363637</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>-1506.5886584198779</v>
@@ -1072,27 +1077,27 @@
         <v>12195</v>
       </c>
       <c r="H11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" t="s">
         <v>5</v>
       </c>
-      <c r="I11" t="s">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
         <v>6</v>
-      </c>
-      <c r="J11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K11" t="s">
-        <v>6</v>
-      </c>
-      <c r="L11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
       </c>
       <c r="C12">
         <v>-1007.5809863718124</v>
@@ -1110,27 +1115,27 @@
         <v>6504</v>
       </c>
       <c r="H12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>-318.85474252272547</v>
@@ -1148,27 +1153,27 @@
         <v>2032.5</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>-79.713685630681383</v>
@@ -1186,27 +1191,27 @@
         <v>406.5</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>-665.93731587650711</v>
@@ -1224,27 +1229,27 @@
         <v>17711.292613636364</v>
       </c>
       <c r="H15" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>6</v>
-      </c>
-      <c r="I15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
       </c>
       <c r="C16">
         <v>-258.47226886060952</v>
@@ -1262,27 +1267,27 @@
         <v>5482.0667613636369</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>-13.776003670119099</v>
@@ -1300,27 +1305,27 @@
         <v>288.52982954545456</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>-2.6492314750229031</v>
@@ -1338,27 +1343,27 @@
         <v>44.389204545454547</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>-404.4641459579542</v>
@@ -1376,27 +1381,27 @@
         <v>7900</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
         <v>6</v>
-      </c>
-      <c r="J19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>8</v>
       </c>
       <c r="C20">
         <v>-212.1096759869786</v>
@@ -1414,27 +1419,27 @@
         <v>2885.294117647059</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>-420.22869002246358</v>
@@ -1452,27 +1457,27 @@
         <v>8230</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>-250.49259578839377</v>
@@ -1490,27 +1495,27 @@
         <v>1596.7339764551994</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <v>-62.623148947098443</v>
@@ -1528,19 +1533,19 @@
         <v>319.34679529103988</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1551,63 +1556,63 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D80CD1-CD30-4052-901D-43B3979F77CA}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>-970.5210144974626</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>-1.4839275036933885</v>
@@ -1616,112 +1621,112 @@
         <v>-2.9877734973692387E-2</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>-1546.9363497933493</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>-10.088310085955754</v>
@@ -1730,36 +1735,36 @@
         <v>-0.21793961527363198</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
         <v>5</v>
       </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>7</v>
-      </c>
       <c r="K6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>-75.568855683948925</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>-6.6591967545296322</v>
@@ -1768,22 +1773,22 @@
         <v>-0.13276047223289916</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
         <v>5</v>
       </c>
-      <c r="K7" t="s">
-        <v>7</v>
-      </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1794,57 +1799,57 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506E853E-93D1-4F94-A4B3-171C15F21EBD}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C3">
         <v>-1808.8873101530066</v>
@@ -1859,22 +1864,22 @@
         <v>-5.1390397419605292E-2</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1885,63 +1890,63 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29054FF7-1F9F-4A7F-A9D6-C626069B2E4E}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>-4876.9219885454231</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>-6.5137304738942357</v>
@@ -1950,36 +1955,36 @@
         <v>-0.14160487679857303</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="K3" t="s">
-        <v>7</v>
-      </c>
       <c r="L3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>-1774.0668084404372</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>-2.3694849046189814</v>
@@ -1988,36 +1993,36 @@
         <v>-5.1511283639903573E-2</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>-950.7241060990475</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>-1.2698092355605342</v>
@@ -2026,36 +2031,36 @@
         <v>-2.7604946363667927E-2</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>-3020.0211762316617</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>-21.407579723539779</v>
@@ -2064,36 +2069,36 @@
         <v>-0.4818824579629139</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>-933.59169847661292</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>-6.6178140973538353</v>
@@ -2102,22 +2107,22 @@
         <v>-0.14896632710272495</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
         <v>5</v>
       </c>
-      <c r="K7" t="s">
-        <v>7</v>
-      </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2128,57 +2133,57 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6070413-1E1D-4202-BEE1-0E3C88ABDAA0}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" t="s">
-        <v>95</v>
-      </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>3566.3983047165029</v>
@@ -2193,30 +2198,30 @@
         <v>0.10422494191183779</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
       <c r="L3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C4">
         <v>2168.1052472696442</v>
@@ -2231,30 +2236,30 @@
         <v>6.3361022563460434E-2</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
       <c r="L4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C5">
         <v>954.4859181741441</v>
@@ -2269,30 +2274,30 @@
         <v>2.5573157299997012E-2</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
       <c r="L5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C6">
         <v>796.8142232743877</v>
@@ -2307,22 +2312,22 @@
         <v>2.1348722995987782E-2</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
         <v>19</v>
       </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2333,46 +2338,46 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C0139C-29C9-42B9-96AA-BECAAAE5830C}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" t="s">
-        <v>94</v>
-      </c>
       <c r="H2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-1498.7846351502469</v>
       </c>
@@ -2386,22 +2391,22 @@
         <v>-0.15897340161396653</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>7</v>
-      </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2412,57 +2417,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91ACFC45-EE67-4E70-9387-1064ADECBEB9}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>46.026241583586391</v>
@@ -2480,27 +2485,27 @@
         <v>601.4130598022</v>
       </c>
       <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
       <c r="L3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>56.401517470719497</v>
@@ -2518,27 +2523,27 @@
         <v>376.5457965878947</v>
       </c>
       <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>36.315541363186675</v>
@@ -2556,27 +2561,27 @@
         <v>603.01158834932892</v>
       </c>
       <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>47.183012855841476</v>
@@ -2594,27 +2599,27 @@
         <v>374.13224309314921</v>
       </c>
       <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
         <v>19</v>
       </c>
-      <c r="I6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>-117.66811971865421</v>
@@ -2632,27 +2637,27 @@
         <v>935.67165053071972</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>-58.765712240573713</v>
@@ -2670,19 +2675,19 @@
         <v>408.40751800909379</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2693,57 +2698,60 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4FB335-AC62-438A-B695-853F9B0C1F56}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>201.2495282251644</v>
@@ -2761,27 +2769,27 @@
         <v>73.655318048838552</v>
       </c>
       <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
       <c r="L3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>159.56040668042198</v>
@@ -2799,27 +2807,27 @@
         <v>98.584872471446161</v>
       </c>
       <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
       <c r="L4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>210.00753749789411</v>
@@ -2837,27 +2845,27 @@
         <v>72.961129718301592</v>
       </c>
       <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
       <c r="L5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>161.11290497719233</v>
@@ -2875,27 +2883,27 @@
         <v>93.601155057927855</v>
       </c>
       <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
         <v>19</v>
       </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
       <c r="L6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>46.25479655211452</v>
@@ -2913,27 +2921,27 @@
         <v>98.375156388798686</v>
       </c>
       <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
         <v>19</v>
       </c>
-      <c r="I7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" t="s">
-        <v>21</v>
-      </c>
       <c r="L7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>3.2585035165094305</v>
@@ -2951,19 +2959,19 @@
         <v>122.19379441268477</v>
       </c>
       <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" t="s">
         <v>19</v>
       </c>
-      <c r="I8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
       <c r="L8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2974,57 +2982,57 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06183DDC-2C81-461B-B6C5-F603EF98DF98}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
       </c>
       <c r="C3">
         <v>-9.9309563361854511</v>
@@ -3042,19 +3050,19 @@
         <v>44.973819334335879</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3065,353 +3073,353 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF52E2A0-46D2-4AAC-88B9-E6FCEF74537B}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3422,57 +3430,57 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC79A2B-BCFC-434A-B881-427155CA3D09}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>-192.73394900542564</v>
@@ -3490,27 +3498,27 @@
         <v>632.79869730411281</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C4">
         <v>-118.27008741302704</v>
@@ -3528,27 +3536,27 @@
         <v>487.2899516282277</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>-296.3310550028155</v>
@@ -3566,27 +3574,27 @@
         <v>117.74015608322394</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>-296.32321941843838</v>
@@ -3604,19 +3612,19 @@
         <v>117.74015608322394</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3627,57 +3635,57 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7C861D3-B2A2-4EBA-B734-EC2845AAA68E}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C3">
         <v>-1977.716792433954</v>
@@ -3692,22 +3700,22 @@
         <v>-5.6186834512101783E-2</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3718,57 +3726,57 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1C4FAF-6C76-4D5B-AC03-B3FA46AF3E52}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>-1915.8359413274577</v>
@@ -3786,19 +3794,19 @@
         <v>6560</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3809,57 +3817,61 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260F638D-C99B-4CA7-915B-B6031A3FA80B}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>-106933.15755961715</v>
@@ -3877,27 +3889,27 @@
         <v>-865054.57133957872</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>-29511.382259391237</v>
@@ -3915,27 +3927,27 @@
         <v>-523427.68681210757</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>-56045.031948099167</v>
@@ -3953,27 +3965,27 @@
         <v>-453386.13573199982</v>
       </c>
       <c r="H5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>-33911.758173217677</v>
@@ -3991,19 +4003,19 @@
         <v>-274335.12765719264</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/costs_outputs.xlsx
+++ b/data/costs_outputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qsi\Desktop\TEA-CART\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/slarue_camsys_com/Documents/Documents/idot_github_puller/TEACART/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07631E1-FFB0-45EC-BD5E-649DDB92E652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E07631E1-FFB0-45EC-BD5E-649DDB92E652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA027505-067A-4249-BACD-239196CEE257}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="774" activeTab="2" xr2:uid="{866DC24D-5F4B-4C41-856A-A432B225A869}"/>
+    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="774" activeTab="9" xr2:uid="{866DC24D-5F4B-4C41-856A-A432B225A869}"/>
   </bookViews>
   <sheets>
     <sheet name="bikeped" sheetId="1" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>New roundabouts</t>
   </si>
   <si>
-    <t>Medium and Heavy Duty Vehicle Replacement (Electrification)</t>
-  </si>
-  <si>
     <t>Light Truck</t>
   </si>
   <si>
@@ -349,6 +346,9 @@
   </si>
   <si>
     <t>Vehicle  Fuel Type</t>
+  </si>
+  <si>
+    <t>Medium- and Heavy-Duty Vehicle Replacement (Electrification)</t>
   </si>
 </sst>
 </file>
@@ -404,9 +404,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -444,7 +444,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -550,7 +550,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -692,7 +692,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -714,40 +714,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
         <v>76</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -1560,53 +1560,53 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
         <v>95</v>
       </c>
-      <c r="B2" t="s">
-        <v>96</v>
-      </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
         <v>55</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
       </c>
       <c r="C3">
         <v>-970.5210144974626</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
@@ -1803,53 +1803,53 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
         <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
       </c>
       <c r="C3">
         <v>-1808.8873101530066</v>
@@ -1894,53 +1894,53 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
         <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
       </c>
       <c r="C3">
         <v>-4876.9219885454231</v>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>-1774.0668084404372</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>-950.7241060990475</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>-3020.0211762316617</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>-933.59169847661292</v>
@@ -2137,53 +2137,53 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
       </c>
       <c r="C3">
         <v>3566.3983047165029</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>2168.1052472696442</v>
@@ -2259,7 +2259,7 @@
         <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>954.4859181741441</v>
@@ -2297,7 +2297,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>796.8142232743877</v>
@@ -2342,39 +2342,39 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
         <v>78</v>
       </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>81</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>82</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>83</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>84</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>85</v>
-      </c>
-      <c r="J2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2426,40 +2426,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -2710,40 +2710,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -2991,40 +2991,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -3082,40 +3082,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -3439,40 +3439,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
         <v>90</v>
       </c>
-      <c r="B2" t="s">
-        <v>91</v>
-      </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -3644,40 +3644,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -3741,34 +3741,34 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -3830,40 +3830,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
         <v>93</v>
       </c>
-      <c r="B2" t="s">
-        <v>94</v>
-      </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>84</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
